--- a/data/trans_dic/IP1022_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen otros</t>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 14,49</t>
+          <t>4,6; 13,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 25,27</t>
+          <t>4,83; 23,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 17,43</t>
+          <t>5,93; 18,77</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,83</t>
+          <t>0,61; 6,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,52</t>
+          <t>4,22; 15,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,8</t>
+          <t>2,95; 8,98</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,22</t>
+          <t>1,39; 10,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 18,16</t>
+          <t>3,53; 18,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,25</t>
+          <t>3,49; 12,44</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 17,03</t>
+          <t>3,6; 18,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,56</t>
+          <t>3,71; 9,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,77</t>
+          <t>4,43; 11,13</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,52</t>
+          <t>2,34; 9,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,75</t>
+          <t>3,56; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,9</t>
+          <t>3,87; 9,02</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,4; 19,29</t>
+          <t>6,58; 19,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 15,82</t>
+          <t>2,17; 13,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 14,12</t>
+          <t>5,1; 14,06</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,43</t>
+          <t>4,84; 9,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,6</t>
+          <t>5,8; 10,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,2</t>
+          <t>5,61; 8,99</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8800</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14443</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23244</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4801; 14546</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6616; 31960</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14321; 45297</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7863</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9982</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>582; 5814</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4031; 15040</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5607; 17092</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7929</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>722; 5651</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2252; 11798</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4034; 14399</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15950</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13046</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28996</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7822; 39183</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7936; 19766</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19128; 48031</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11084</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17110</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2792; 11268</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5794; 18011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10903; 25447</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7951</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12420</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4535; 13203</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1563; 10012</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7185; 19804</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>43066</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>56615</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>99681</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>31803; 61746</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>43177; 77298</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>78679; 126078</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1022_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,92</t>
+          <t>4,58; 14,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 23,34</t>
+          <t>4,9; 24,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 18,77</t>
+          <t>5,98; 17,05</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,14</t>
+          <t>0,62; 6,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 15,74</t>
+          <t>3,99; 14,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,98</t>
+          <t>2,98; 9,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 10,9</t>
+          <t>1,27; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 18,48</t>
+          <t>3,84; 18,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 12,44</t>
+          <t>3,71; 13,11</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 18,02</t>
+          <t>3,41; 15,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,23</t>
+          <t>3,78; 9,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,13</t>
+          <t>4,58; 11,16</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,44</t>
+          <t>2,32; 9,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,08</t>
+          <t>3,73; 10,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,02</t>
+          <t>4,07; 9,27</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 19,16</t>
+          <t>6,15; 19,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,91</t>
+          <t>2,16; 14,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 14,06</t>
+          <t>5,11; 13,67</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,4</t>
+          <t>4,74; 9,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,38</t>
+          <t>5,79; 10,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,99</t>
+          <t>5,74; 9,0</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4801; 14546</t>
+          <t>4788; 15236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6616; 31960</t>
+          <t>6707; 33179</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14321; 45297</t>
+          <t>14424; 41164</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>582; 5814</t>
+          <t>588; 6466</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4031; 15040</t>
+          <t>3809; 13754</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5607; 17092</t>
+          <t>5660; 17961</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>722; 5651</t>
+          <t>656; 5417</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2252; 11798</t>
+          <t>2452; 12060</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4034; 14399</t>
+          <t>4295; 15165</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7822; 39183</t>
+          <t>7410; 34525</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7936; 19766</t>
+          <t>8081; 20099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19128; 48031</t>
+          <t>19741; 48169</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2792; 11268</t>
+          <t>2770; 11352</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5794; 18011</t>
+          <t>6062; 17654</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10903; 25447</t>
+          <t>11474; 26141</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4535; 13203</t>
+          <t>4240; 13202</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1563; 10012</t>
+          <t>1552; 10543</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7185; 19804</t>
+          <t>7202; 19266</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31803; 61746</t>
+          <t>31121; 64259</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43177; 77298</t>
+          <t>43118; 76875</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78679; 126078</t>
+          <t>80452; 126160</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 14,58</t>
+          <t>3,94; 12,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 24,23</t>
+          <t>4,79; 15,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 17,05</t>
+          <t>5,14; 11,7</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,83</t>
+          <t>4,21; 15,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 14,39</t>
+          <t>0,58; 5,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 9,44</t>
+          <t>2,94; 8,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,44</t>
+          <t>3,41; 16,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 18,89</t>
+          <t>1,12; 11,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,11</t>
+          <t>3,24; 10,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,88</t>
+          <t>3,86; 9,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,39</t>
+          <t>3,78; 10,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,16</t>
+          <t>4,68; 8,89</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,51</t>
+          <t>3,76; 11,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,86</t>
+          <t>2,69; 10,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,27</t>
+          <t>4,0; 9,14</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 19,16</t>
+          <t>2,13; 15,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,64</t>
+          <t>6,42; 19,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,67</t>
+          <t>5,22; 14,5</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,78</t>
+          <t>5,48; 8,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,32</t>
+          <t>5,0; 8,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,0</t>
+          <t>5,61; 8,03</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>17945</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4788; 15236</t>
+          <t>4826; 15110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6707; 33179</t>
+          <t>4934; 15514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14424; 41164</t>
+          <t>11582; 26390</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9871</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>588; 6466</t>
+          <t>3848; 13849</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3809; 13754</t>
+          <t>556; 5699</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5660; 17961</t>
+          <t>5518; 16551</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7041</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>656; 5417</t>
+          <t>1943; 9618</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2452; 12060</t>
+          <t>600; 5921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4295; 15165</t>
+          <t>3580; 12068</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>23599</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7410; 34525</t>
+          <t>7622; 18670</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8081; 20099</t>
+          <t>6741; 18571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19741; 48169</t>
+          <t>17590; 33401</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16780</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2770; 11352</t>
+          <t>5575; 16538</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6062; 17654</t>
+          <t>3200; 12111</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11474; 26141</t>
+          <t>10691; 24413</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>12341</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4240; 13202</t>
+          <t>1455; 10883</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1552; 10543</t>
+          <t>4517; 14031</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7202; 19266</t>
+          <t>7243; 20110</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>43066</t>
+          <t>48037</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>56615</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99681</t>
+          <t>87577</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31121; 64259</t>
+          <t>37519; 60576</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43118; 76875</t>
+          <t>30983; 51240</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80452; 126160</t>
+          <t>73207; 104790</t>
         </is>
       </c>
     </row>
